--- a/data/Gearbox Design Guide Data.xlsx
+++ b/data/Gearbox Design Guide Data.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://atlanticbearing-my.sharepoint.com/personal/rishi_sivakumar_atlantic-bearing_com/Documents/Documents/GitHub/Gearbox Design/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://atlanticbearing-my.sharepoint.com/personal/rishi_sivakumar_atlantic-bearing_com/Documents/Documents/GitHub/Gear-Automation/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A1DB845-6C1E-4D0F-97F1-0B4EDB7910C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{4A1DB845-6C1E-4D0F-97F1-0B4EDB7910C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2DE694D-E0DC-44D4-B715-5FB8B5DD8F1C}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{C881B644-CB8F-4B90-AB0E-C67886A8E4B5}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{C881B644-CB8F-4B90-AB0E-C67886A8E4B5}"/>
   </bookViews>
   <sheets>
-    <sheet name="SEN - Stage2" sheetId="1" r:id="rId1"/>
-    <sheet name="SZN - Stage3" sheetId="2" r:id="rId2"/>
-    <sheet name="SDN - Stage4" sheetId="3" r:id="rId3"/>
+    <sheet name="SEN - Stage1" sheetId="1" r:id="rId1"/>
+    <sheet name="SZN - Stage2" sheetId="2" r:id="rId2"/>
+    <sheet name="SDN - Stage3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
